--- a/tests/workbooktests/workbooks/test_interpolatedyieldcurves.xlsx
+++ b/tests/workbooktests/workbooks/test_interpolatedyieldcurves.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6040C8B3-F6D7-4C29-886D-5CB5082C2014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DCFB23-D902-44CE-BA3F-C3F0A7116255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="-19800" windowWidth="28800" windowHeight="18120" xr2:uid="{5088EC6F-18E0-4AC9-9BC5-4CE1169B8F7F}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{5088EC6F-18E0-4AC9-9BC5-4CE1169B8F7F}"/>
   </bookViews>
   <sheets>
     <sheet name="qlInterpolatedYieldCurve" sheetId="1" r:id="rId1"/>
@@ -533,7 +533,7 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <f ca="1">TODAY()</f>
-        <v>46166</v>
+        <v>46230</v>
       </c>
       <c r="C5" s="2">
         <f ca="1">EXP(-$C$2*(B5-$B$5)/365)</f>
@@ -547,7 +547,7 @@
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <f ca="1">B5+365</f>
-        <v>46531</v>
+        <v>46595</v>
       </c>
       <c r="C6" s="2">
         <f ca="1">EXP(-$C$2*(B6-$B$5)/365)</f>
@@ -561,7 +561,7 @@
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <f ca="1">B6+365</f>
-        <v>46896</v>
+        <v>46960</v>
       </c>
       <c r="C7" s="2">
         <f ca="1">EXP(-$C$2*(B7-$B$5)/365)</f>
@@ -575,7 +575,7 @@
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <f ca="1">B7+365</f>
-        <v>47261</v>
+        <v>47325</v>
       </c>
       <c r="C8" s="2">
         <f ca="1">EXP(-$C$2*(B8-$B$5)/365)</f>
@@ -589,7 +589,7 @@
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <f ca="1">B8+365</f>
-        <v>47626</v>
+        <v>47690</v>
       </c>
       <c r="C9" s="2">
         <f ca="1">EXP(-$C$2*(B9-$B$5)/365)</f>

--- a/tests/workbooktests/workbooks/test_interpolatedyieldcurves.xlsx
+++ b/tests/workbooktests/workbooks/test_interpolatedyieldcurves.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DCFB23-D902-44CE-BA3F-C3F0A7116255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8DF0BA-D446-44AA-B300-0D74EA0F58AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{5088EC6F-18E0-4AC9-9BC5-4CE1169B8F7F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5088EC6F-18E0-4AC9-9BC5-4CE1169B8F7F}"/>
   </bookViews>
   <sheets>
     <sheet name="qlInterpolatedYieldCurve" sheetId="1" r:id="rId1"/>
@@ -503,7 +503,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38FE1B30-2282-4CB0-BC3A-F4A304EAB6FC}">
-  <dimension ref="A2:D41"/>
+  <dimension ref="A2:D40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -533,7 +533,7 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46245</v>
       </c>
       <c r="C5" s="2">
         <f ca="1">EXP(-$C$2*(B5-$B$5)/365)</f>
@@ -547,7 +547,7 @@
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <f ca="1">B5+365</f>
-        <v>46595</v>
+        <v>46610</v>
       </c>
       <c r="C6" s="2">
         <f ca="1">EXP(-$C$2*(B6-$B$5)/365)</f>
@@ -561,7 +561,7 @@
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <f ca="1">B6+365</f>
-        <v>46960</v>
+        <v>46975</v>
       </c>
       <c r="C7" s="2">
         <f ca="1">EXP(-$C$2*(B7-$B$5)/365)</f>
@@ -575,7 +575,7 @@
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <f ca="1">B7+365</f>
-        <v>47325</v>
+        <v>47340</v>
       </c>
       <c r="C8" s="2">
         <f ca="1">EXP(-$C$2*(B8-$B$5)/365)</f>
@@ -589,7 +589,7 @@
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <f ca="1">B8+365</f>
-        <v>47690</v>
+        <v>47705</v>
       </c>
       <c r="C9" s="2">
         <f ca="1">EXP(-$C$2*(B9-$B$5)/365)</f>
@@ -732,41 +732,35 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C36" t="str" cm="1">
-        <f t="array" aca="1" ref="C36" ca="1">_xll.qlInterpolatedYieldCurve($B$5:$B$9,$C$5:$C$9,$C$11,$C$12,$C$16,C20)</f>
+        <f t="array" aca="1" ref="C36" ca="1">_xll.qlInterpolatedYieldCurve($B$5:$B$9,$C$5:$C$9,$C$11,$C$12,$C$16,C23)</f>
         <v>欣[test_interpolatedyieldcurves.xlsx]qlInterpolatedYieldCurve!R36C3YieldTermStructureHandle,A</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C37" t="str" cm="1">
-        <f t="array" aca="1" ref="C37" ca="1">_xll.qlInterpolatedYieldCurve($B$5:$B$9,$C$5:$C$9,$C$11,$C$12,$C$16,C23)</f>
-        <v>欣[test_interpolatedyieldcurves.xlsx]qlInterpolatedYieldCurve!R37C3YieldTermStructureHandle,A</v>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" t="str" cm="1">
+        <f t="array" aca="1" ref="C38" ca="1">_xll.qlDiscountCurve(B5:B9,C5:C9)</f>
+        <v>欣[test_interpolatedyieldcurves.xlsx]qlInterpolatedYieldCurve!R38C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C39" t="str" cm="1">
-        <f t="array" aca="1" ref="C39" ca="1">_xll.qlDiscountCurve(B5:B9,C5:C9)</f>
+        <f t="array" aca="1" ref="C39" ca="1">_xll.qlForwardCurve(B5:B9,D5:D9,C11)</f>
         <v>欣[test_interpolatedyieldcurves.xlsx]qlInterpolatedYieldCurve!R39C3YieldTermStructureHandle,A</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" t="str" cm="1">
-        <f t="array" aca="1" ref="C40" ca="1">_xll.qlForwardCurve(B5:B9,D5:D9,C11)</f>
+        <f t="array" aca="1" ref="C40" ca="1">_xll.qlZeroCurve(B5:B9,D5:D9,,C12)</f>
         <v>欣[test_interpolatedyieldcurves.xlsx]qlInterpolatedYieldCurve!R40C3YieldTermStructureHandle,A</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" t="str" cm="1">
-        <f t="array" aca="1" ref="C41" ca="1">_xll.qlZeroCurve(B5:B9,D5:D9,,C12)</f>
-        <v>欣[test_interpolatedyieldcurves.xlsx]qlInterpolatedYieldCurve!R41C3YieldTermStructureHandle,A</v>
       </c>
     </row>
   </sheetData>
